--- a/output/OR202603121104075460_price_match.xlsx
+++ b/output/OR202603121104075460_price_match.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,10 +29,32 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,11 +63,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F4858"/>
+        <fgColor rgb="001F3650"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3EA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -53,16 +85,92 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="00538135"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00538135"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,381 +536,1700 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Henry Schein Price Match Negotiation  ·  Ref: OR202603121104075460  ·  Date: 03/12/2026  ·  Patient: —  ·  Generated: 2026-06-12 16:39</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>🟢 &gt;10% savings   🟡 5–10% savings   Main row = best option (EXACT when available) · ↳ Option 2-3 = next-closest matches with reasoning · GATED = login/membership pricing, verify manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
           <t>Schein SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Manufacturer Part Number</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturer Part
+Number</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Qty Ordered</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Schein Unit Price</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Best Public Price</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Qty
+Order</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Schein Unit
+Price</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Best Public Price
+Found</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Match Score</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Source Site</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Product URL</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Qty/Pack Condition</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Savings Per Unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Product URL Link</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Pack/Qty Condition
+(e.g. "6-pack price")</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Why Not Exact / Notes</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Savings Per
+Unit</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>Total Savings</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>7772551</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>278.99</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>137.49</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (81%)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Safco Dental Supply</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>https://www.safcodental.com/product/3m-sup-trade-sup-clinpro-sup-trade-sup-clear-fluoride-treatment</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Not exact — mismatch on: product name · Different variant (mint flavor)</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>707.5</v>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="10" t="inlineStr"/>
+      <c r="B5" s="10" t="inlineStr"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="12" t="n">
+        <v>294.99</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (83%)</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Dental City</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.dentalcity.com/product/21837/3m-clinpro-clear-fluoride-varnish-100pack</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>Buy 4, Get 1 Free</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>Not exact — mismatch on: product name · Different variant (Mint flavor)</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>-16</v>
+      </c>
+      <c r="M5" s="12" t="n">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="10" t="inlineStr"/>
+      <c r="B6" s="10" t="inlineStr"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="12" t="n">
+        <v>267.97</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (81%)</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/clinpro-clear-21-sodium-fluoride-treatment-05-d-182709</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>Not exact — mismatch on: product name · Different variant (Watermelon flavor) and scraped product name includes flavor</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>5703375</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D7" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E7" s="7" t="n">
         <v>29.46</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F7" s="7" t="n">
         <v>5.99</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>pricenex.com</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://pricenex.com/denture-boxes-assorted-12-bx/?srsltid=AfmBOopifgWtTcdb8uYUsTJmWmNTHndZRniQTerYWQCPC7Bb_1P_cxtW</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Pricenex</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>https://pricenex.com/denture-boxes-assorted-12-bx/</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="n">
         <v>23.47</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="M7" s="9" t="n">
         <v>352.05</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="10" t="inlineStr"/>
+      <c r="B8" s="10" t="inlineStr"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr"/>
+      <c r="F8" s="12" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Dent-Shur-Cups-MI400</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>274.65</v>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="10" t="inlineStr"/>
+      <c r="B9" s="10" t="inlineStr"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="12" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Dental City</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>https://dentalcity.com/product/9911/dental-city-denture-boxes-12pack</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>274.35</v>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>5703169</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>222.77</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Perfect-Choice-Prophy-Angles-514650</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Quantity discounts available</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>Not exact — mismatch on: brand · Different brand, but same product family</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>68.87</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>206.61</v>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="10" t="inlineStr"/>
+      <c r="B11" s="10" t="inlineStr"/>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
+      <c r="E11" s="10" t="inlineStr"/>
+      <c r="F11" s="12" t="n">
+        <v>263.85</v>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (73%)</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Core-Elite-Flex-Disposable-Prophy-Angle-500-Pk</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>Not exact — mismatch on: brand · Different brand, but same product family</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>-41.08</v>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>-123.24</v>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="10" t="inlineStr"/>
+      <c r="B12" s="10" t="inlineStr"/>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
+      <c r="E12" s="10" t="inlineStr"/>
+      <c r="F12" s="12" t="n">
+        <v>355.09</v>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (79%)</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Dental City</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>https://dentalcity.com/product/13289/denticator-disposable-prophy-angles-500pack</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>Not exact — mismatch on: brand · Different brand, but same product family and variant is similar</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>-132.32</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>-396.96</v>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>1469109</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D13" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E13" s="7" t="n">
         <v>24.31</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F13" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Pricenex</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>https://pricenex.com/barrier-film-4-x-6-blue-roll-of-1200-sheets/</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Buy 5 - 9 at $4.85 each</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>194.1</v>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="10" t="inlineStr"/>
+      <c r="B14" s="10" t="inlineStr"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+      <c r="E14" s="10" t="inlineStr"/>
+      <c r="F14" s="12" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/primo-4-x-6-barrier-film-blue-d-162058</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>153.2</v>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="10" t="inlineStr"/>
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="12" t="n">
         <v>11.99</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>skydentalsupply.com</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://www.skydentalsupply.com/100z-barrier-film.htm?srsltid=AfmBOoq90XYlzy1A1Qq52vUJgmUCtD-yGlX-cJ0S5-agvGuv7KGqze_X</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1 unit</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>https://www.skydentalsupply.com/100z-barrier-film.htm</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Minimal quantity for this product is 1</t>
+        </is>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="n">
         <v>12.32</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="M15" s="12" t="n">
         <v>123.2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>1126863</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Frontier Dental Supply</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>https://frontierdental.com/us/en/product/hp-mixing-tips-42-mm-yellow-48pk-100623-160524?promo=YmFubmVyX2FkczoxMDYw</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>84.04000000000001</v>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="10" t="inlineStr"/>
+      <c r="B17" s="10" t="inlineStr"/>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="12" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/mark3-high-performance-mixing-tips-42-mm-d-157605</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>Not exact — mismatch on: brand · Different brand, but same product family</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>43.32</v>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="10" t="inlineStr"/>
+      <c r="B18" s="10" t="inlineStr"/>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr"/>
+      <c r="F18" s="12" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Chase Dental Supply</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>https://chasedentalsupply.com/mark3-t-style-short-hp-mixing-tips-yellow-4-2mm-48-pk/</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>Not exact — mismatch on: brand · Different brand, but same product family</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>-5.54</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>-22.16</v>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>2906663</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E19" s="7" t="n">
         <v>82.19</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F19" s="7" t="n">
         <v>64.89</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>net32.com</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (96%)</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/luxatemp-automix-plus-fine-mixing-tips-25-d-45565</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="n">
         <v>17.3</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="M19" s="9" t="n">
         <v>69.2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="10" t="inlineStr"/>
+      <c r="B20" s="10" t="inlineStr"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
+      <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="12" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Luxatemp-Automix-Plus-110351</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>69.04000000000001</v>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="10" t="inlineStr"/>
+      <c r="B21" s="10" t="inlineStr"/>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr"/>
+      <c r="F21" s="12" t="n">
+        <v>64.95</v>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (96%)</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>The Dental Market U.S.</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>https://thedentalmarket.net/featured-items/luxatemp-automix-plus-fine-mixing-tips-box-of-25/</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>68.95999999999999</v>
+      </c>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>3120099</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>144.39</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>122</v>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/purevac-sc-evacuation-system-cleaner-5-liter169-d-143563</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>Not exact — mismatch on: product name · Different variant (citrus scent), but same product family</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="M22" s="9" t="n">
+        <v>44.78</v>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>3250497</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E23" s="7" t="n">
         <v>16.62</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F23" s="7" t="n">
         <v>11.25</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>curio.dental</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://curio.dental/products/oral-b-glide-floss-160m-2-bx-unflavored?srsltid=AfmBOooXT8whakmYGUzMjYZwXh3xkF8BLdTQYtiihyk9mnF_nRd4tEEv</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (98%)</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Pro-Health-Glide-Floss-Procter-Gamble-80779742</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Quantity discounts available</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="n">
         <v>5.37</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="M23" s="9" t="n">
         <v>26.85</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="10" t="inlineStr"/>
+      <c r="B24" s="10" t="inlineStr"/>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+      <c r="E24" s="10" t="inlineStr"/>
+      <c r="F24" s="12" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (98%)</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>The Dental Market U.S.</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>https://thedentalmarket.net/preventives/oral-b-glide-healthy-gums-in-office-floss-refill-unflavored-160-m-2-box/</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>13.35</v>
+      </c>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="10" t="inlineStr"/>
+      <c r="B25" s="10" t="inlineStr"/>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
+      <c r="E25" s="10" t="inlineStr"/>
+      <c r="F25" s="12" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (66%)</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>https://www.target.com/p/up-up-2-count-160-count-each-floss-picks-mint/-/A-94981365</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Save $0.48 (5% off) when purchased as a bundle.</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>Not exact — mismatch on: brand, product name · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>5701400</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D26" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E26" s="7" t="n">
         <v>17.61</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F26" s="7" t="n">
         <v>10.99</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>supplyclinic.com</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://www.supplyclinic.com/items/3cc-luer-lock-disposable-syringes-non-sterile-box-of-100-plastcare-usa-pg-s3cc?srsltid=AfmBOorHCKut6hb1-oAwLg19Hf5boZY_CDln3r9eNI9HLDJA0HiHXg8f</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Supply Clinic</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/3cc-luer-lock-disposable-syringes-non-sterile-box-of-100-plastcare-usa-pg-s3cc</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>Backordered</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="n">
         <v>6.62</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="M26" s="9" t="n">
         <v>13.24</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="10" t="inlineStr"/>
+      <c r="B27" s="10" t="inlineStr"/>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr"/>
+      <c r="F27" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>GATED (0%)</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Bound Tree Medical</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>https://www.boundtree.com/iv-drug-delivery/syringes-needles/syringes-with-needle-luer-lock-tip-3cc/p/group002614</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>GATED — pricing requires login/membership on this site; price shown comes from the public search listing. Verify manually before negotiating.</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>34.62</v>
+      </c>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="10" t="inlineStr"/>
+      <c r="B28" s="10" t="inlineStr"/>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="inlineStr"/>
+      <c r="F28" s="12" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>GATED (0%)</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Vitality Medical</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>https://www.vitalitymedical.com/3-ml-syringe-without-needle.html</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>GATED — pricing requires login/membership on this site; price shown comes from the public search listing. Verify manually before negotiating.</t>
+        </is>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>-17.78</v>
+      </c>
+      <c r="M28" s="12" t="n">
+        <v>-35.56</v>
+      </c>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (98%)</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Benco Dental</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>https://shop.benco.com/Product/3168-583/3m-clinpro-sealant-refill-12ml-syringe</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>-11.29</v>
+      </c>
+      <c r="M29" s="15" t="n">
+        <v>-22.58</v>
+      </c>
+    </row>
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="10" t="inlineStr"/>
+      <c r="B30" s="10" t="inlineStr"/>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
+      <c r="E30" s="10" t="inlineStr"/>
+      <c r="F30" s="12" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>GATED (0%)</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Supply Clinic</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/3m-clinpro-sealant-introductory-kit-12626-1-2-ml-syringe-2-syringes-kit-3m-12626</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>GATED — pricing requires login/membership on this site; price shown comes from the public search listing. Verify manually before negotiating.</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="M30" s="12" t="n">
+        <v>29.32</v>
+      </c>
+    </row>
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>5700360</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>zoro.com</t>
+        </is>
+      </c>
+      <c r="I31" s="19" t="inlineStr">
+        <is>
+          <t>https://www.zoro.com/benzo-jel-topical-anesthetic-strawberry-1oz-00404003330/i/G622895661/</t>
+        </is>
+      </c>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L31" s="18" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="M31" s="20" t="n">
+        <v>-21.2</v>
+      </c>
+    </row>
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="10" t="inlineStr"/>
+      <c r="B32" s="10" t="inlineStr"/>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr"/>
+      <c r="F32" s="12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Davis Dental Supply</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>https://www.davisdentalsupply.com/products/productcode-d332019</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>Not exact — mismatch on: brand · Different brand, but same product type</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="M32" s="12" t="n">
+        <v>13.36</v>
+      </c>
+    </row>
+    <row r="33" ht="56" customHeight="1">
+      <c r="A33" s="10" t="inlineStr"/>
+      <c r="B33" s="10" t="inlineStr"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (58%)</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Topical-Anesthetic-Gel-AN304_2</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Quantity discounts available</t>
+        </is>
+      </c>
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>Not exact — mismatch on: brand, product name · Different brand and product name, but same product family</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>7.16</v>
+      </c>
+    </row>
+    <row r="34" ht="56" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>1459489</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D34" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E34" s="12" t="n">
         <v>120.37</v>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>113.99</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ddsdentalsupplies.com</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://ddsdentalsupplies.com/silhouette-low-profile-nasal-m/?srsltid=AfmBOooP2vWoCNQYo-sPWRslM_SyTQAGxTHywy6-7c62HP5n9zdAgtzD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>12.76</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>27.88</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>supplyclinic.com</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://www.supplyclinic.com/items/3m-clinpro-sealant-refill-12627-1-2-ml-syringe-1-syringe-pack-3m-12627?srsltid=AfmBOoqBuCw8O_rwDmMxaQtnT_Qo0mt8IwdcJK4nzLblRieoCM4IafTG</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>LICENSE REQUIRED</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>8.640000000000001</v>
+      <c r="F34" s="12" t="n">
+        <v>140.08</v>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>GATED (0%)</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Supply Clinic</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/silhouette-low-profile-nasal-masks-medium-12-pack-porter-instrument-division-sil-med-12</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>GATED — pricing requires login/membership on this site; price shown comes from the public search listing. Verify manually before negotiating.</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>-19.71</v>
+      </c>
+      <c r="M34" s="15" t="n">
+        <v>-39.42</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/OR202603121104075460_price_match.xlsx
+++ b/output/OR202603121104075460_price_match.xlsx
@@ -54,7 +54,7 @@
       <color rgb="007F7F7F"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -68,17 +68,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00EAF3EA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF3EA"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -171,24 +166,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -556,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -577,7 +554,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Henry Schein Price Match Negotiation  ·  Ref: OR202603121104075460  ·  Date: 03/12/2026  ·  Patient: —  ·  Generated: 2026-06-13 16:46</t>
+          <t>Henry Schein Price Match Negotiation  ·  Ref: OR202603121104075460  ·  Date: 03/12/2026  ·  Patient: —  ·  Generated: 2026-06-13 20:08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -676,7 +653,7 @@
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>7772551</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -686,36 +663,36 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>29.46</v>
+        <v>278.99</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>5.99</v>
+        <v>267.97</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>EXACT (100%)</t>
+          <t>EXACT (96%)</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Pricenex</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>https://pricenex.com/denture-boxes-assorted-12-bx/</t>
+          <t>https://www.net32.com/ec/clinpro-clear-21-sodium-fluoride-treatment-05-d-182709</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 @ $267.97,  2 @ $256.98</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -724,10 +701,10 @@
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>23.47</v>
+        <v>11.02</v>
       </c>
       <c r="M4" s="9" t="n">
-        <v>352.05</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
@@ -741,38 +718,38 @@
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="10" t="inlineStr"/>
       <c r="F5" s="12" t="n">
-        <v>9.029999999999999</v>
+        <v>133.95</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>EXACT (100%)</t>
+          <t>APPROXIMATE (77%)</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Scott's Dental Supply</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/denture-storage-boxes-assorted-12-pk-hsb-house-brand-dentistry-100010</t>
+          <t>https://www.scottsdental.com/3m-clinpro-clear-fluoride-treatment.html</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>Add $10 for free shipping from Frontier Dental Supply Inc.</t>
+          <t>Smaller pack size</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+          <t>PACK MISMATCH (page 50 vs ordered 100) · VARIANT MISMATCH (ordered: No Flavor) · Matching: brand, product name, form/spec · Not matching: pack size · Different pack quantity (50 vs 100) and flavor (Mint vs No Flavor)</t>
         </is>
       </c>
       <c r="L5" s="12" t="n">
-        <v>20.43</v>
+        <v>145.04</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>306.45</v>
+        <v>725.2</v>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
@@ -786,21 +763,21 @@
       <c r="D6" s="10" t="inlineStr"/>
       <c r="E6" s="10" t="inlineStr"/>
       <c r="F6" s="12" t="n">
-        <v>11.17</v>
+        <v>182.99</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>EXACT (100%)</t>
+          <t>POSSIBLE (40%)</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>https://www.dentalcity.com/product/9911/dental-city-denture-boxes</t>
+          <t>https://www.net32.com/ec/locator-replacement-denture-cap-male-assembly-10-d-178963</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
@@ -810,128 +787,116 @@
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+          <t>PACK MISMATCH (page 10 vs ordered 100) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: No Flavor) · Not matching: brand, product name, form/spec, pack size · Completely different product</t>
         </is>
       </c>
       <c r="L6" s="12" t="n">
-        <v>18.29</v>
+        <v>96</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>274.35</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>5703169</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="17" t="n">
         <v>222.77</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="17" t="n">
         <v>153.9</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>GENERIC EQUIVALENT (79%)</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>Crazy Dental Price Club</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/Perfect-Choice-Prophy-Angles-514650</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>Quantity discounts available</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t>GENERIC EQUIVALENT — same product type, different/no brand; no competitor sells the exact Schein house-brand item. Verify clinical equivalence before substituting.</t>
         </is>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="L7" s="17" t="n">
         <v>68.87</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="19" t="n">
         <v>206.61</v>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>1469109</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>24.31</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>EXACT (96%)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Dental Mates</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>https://dentalmates.com/products/dental-barrier-film-sticky-wrap-in-blue-4-x-6-1200-sheet</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>One Roll or 8 Rolls Case</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>14.32</v>
-      </c>
-      <c r="M8" s="9" t="n">
-        <v>143.2</v>
+      <c r="A8" s="10" t="inlineStr"/>
+      <c r="B8" s="10" t="inlineStr"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr"/>
+      <c r="F8" s="12" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (62%)</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Safco Dental Supply</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>https://www.safcodental.com/product/safco-cleancare-trade-disposable-prophy-angles</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>Smaller pack size</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 100 vs ordered 500) · Matching: product name, form/spec · Not matching: brand, pack size · Different brand and pack quantity</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>195.78</v>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>587.34</v>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
@@ -939,146 +904,146 @@
       <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
+          <t xml:space="preserve">   ↳ Option 3</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
       <c r="E9" s="10" t="inlineStr"/>
       <c r="F9" s="12" t="n">
-        <v>10.5</v>
+        <v>71.86</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>EXACT (98%)</t>
+          <t>POSSIBLE (68%)</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/barrier-film-4x6-1200-sheets-blue-sky-dental-supply-ky100z</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Preventives/Prophy-Products/Prophy-Angles/c/445/manufacturer/ACCLEAN%20by%20Henry%20Schein</t>
         </is>
       </c>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>Add $200 for free shipping from Sky Dental Supply</t>
+          <t>Smaller pack size</t>
         </is>
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+          <t>PACK MISMATCH (page 100 vs ordered 500) · VARIANT MISMATCH (ordered: Soft Short Gray) · Matching: brand, form/spec · Not matching: product name, pack size · Different product name and pack quantity</t>
         </is>
       </c>
       <c r="L9" s="12" t="n">
-        <v>13.81</v>
+        <v>150.91</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>138.1</v>
+        <v>452.73</v>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="10" t="inlineStr"/>
-      <c r="B10" s="10" t="inlineStr"/>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 3</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="12" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>EXACT (96%)</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>skydentalsupply.com</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>https://www.skydentalsupply.com/100z-barrier-film.htm</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="14" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="M10" s="12" t="n">
-        <v>123.2</v>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>5703375</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Pricenex</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>https://pricenex.com/denture-boxes-assorted-12-bx/</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="M10" s="19" t="n">
+        <v>352.05</v>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2906663</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>82.19</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>64.89</v>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>EXACT (98%)</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Net32</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>https://www.net32.com/ec/luxatemp-automix-plus-fine-mixing-tips-25-d-45565</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="M11" s="9" t="n">
-        <v>69.2</v>
+      <c r="A11" s="10" t="inlineStr"/>
+      <c r="B11" s="10" t="inlineStr"/>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
+      <c r="E11" s="10" t="inlineStr"/>
+      <c r="F11" s="12" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>DDS Dental Supplies</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>https://ddsdentalsupplies.com/preventives/</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 12 vs ordered 12) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Assorted) · Not matching: brand, product name, form/spec, pack size · Different product</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>328.05</v>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
@@ -1086,13 +1051,13 @@
       <c r="B12" s="10" t="inlineStr"/>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
+          <t xml:space="preserve">   ↳ Option 3</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
       <c r="E12" s="10" t="inlineStr"/>
       <c r="F12" s="12" t="n">
-        <v>64.93000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -1101,17 +1066,17 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Frontier Dental Supply</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Luxatemp-Automix-Plus-110351</t>
+          <t>https://www.frontierdental.com/us/en/product/denture-storage-boxes-assorted-12pk-100010-161115</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>This item requires special handling - a small fee will be applied once per order during checkout.</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
@@ -1120,112 +1085,112 @@
         </is>
       </c>
       <c r="L12" s="12" t="n">
-        <v>17.26</v>
+        <v>21.61</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>69.04000000000001</v>
+        <v>324.15</v>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="10" t="inlineStr"/>
-      <c r="B13" s="10" t="inlineStr"/>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 3</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
-      <c r="E13" s="10" t="inlineStr"/>
-      <c r="F13" s="12" t="n">
-        <v>75.04000000000001</v>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>EXACT (98%)</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>MVP Dental Supply</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>https://mvpdentalsupply.com/products/dmg-america-110351-luxatemp-plus-mixing-tips-fine-pk-25</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K13" s="14" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="M13" s="12" t="n">
-        <v>28.6</v>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>2906663</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>82.19</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>EXACT (92%)</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>Supply Clinic</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/luxatemp-plus-mixing-tips-fine-25-bx-dmg-america-110351</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L13" s="17" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="M13" s="19" t="n">
+        <v>95.68000000000001</v>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>1126863</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>34.29</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>GENERIC EQUIVALENT (73%)</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>jobs.pfefferwerk.de</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>https://jobs.pfefferwerk.de/products/practicon-hp-universal-mixing-tips-yellow-42mm-pack-of-48</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>GENERIC EQUIVALENT — same product type, different/no brand; no competitor sells the exact Schein house-brand item. Verify clinical equivalence before substituting.</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="M14" s="9" t="n">
-        <v>53.96</v>
+      <c r="A14" s="10" t="inlineStr"/>
+      <c r="B14" s="10" t="inlineStr"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+      <c r="E14" s="10" t="inlineStr"/>
+      <c r="F14" s="12" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (51%)</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Anson Dental Supply</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>https://ansondental.com/products/intra-oral-mixing-tips-for-brown-tips-25-pcs-pk</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Fine) · Matching: pack size · Not matching: brand, product name, form/spec · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>280.8</v>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
@@ -1233,27 +1198,27 @@
       <c r="B15" s="10" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
+          <t xml:space="preserve">   ↳ Option 3</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr"/>
       <c r="E15" s="10" t="inlineStr"/>
       <c r="F15" s="12" t="n">
-        <v>39.73</v>
+        <v>13.99</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>EXACT (92%)</t>
+          <t>POSSIBLE (36%)</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>oktowallz.com</t>
         </is>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Dispensing-%26-Mixing-Products/Dispensing-Products/Mixing-Tips/Maxima-HP-High-Performance-Mixing/p/180785-3</t>
+          <t>https://oktowallz.com/view/Orange-Pack-Of-49-Disposable-Tips-For-Dental-Impression/833810</t>
         </is>
       </c>
       <c r="J15" s="14" t="inlineStr">
@@ -1263,20 +1228,20 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+          <t>PACK MISMATCH (page 49 vs ordered 25) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Fine) · Not matching: brand, product name, form/spec, pack size · Different product and pack quantity</t>
         </is>
       </c>
       <c r="L15" s="12" t="n">
-        <v>-5.44</v>
+        <v>68.2</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>-21.76</v>
+        <v>272.8</v>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1286,219 +1251,1167 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="7" t="n">
+        <v>144.39</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>194.45</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>US Dental Depot</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>https://usdentaldepot.com/purevac-sc-evacuation-system-cleane-dentsply-21135</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>-50.06</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>-100.12</v>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="10" t="inlineStr"/>
+      <c r="B17" s="10" t="inlineStr"/>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="12" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (51%)</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>skydentalsupply.com</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.skydentalsupply.com/evac-cleaner/</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>BUY 3 GET 1 FREE</t>
+        </is>
+      </c>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: specified) · Matching: pack size · Not matching: brand, product name, form/spec · Different brand and product name, also variant 'Sable' does not match</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>208.8</v>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="10" t="inlineStr"/>
+      <c r="B18" s="10" t="inlineStr"/>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr"/>
+      <c r="F18" s="12" t="n">
+        <v>197.73</v>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Dental City</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>https://www.dentalcity.com/product/11656/dentsply-sirona-purevac-sc-evacuation-system-cleaner-5l</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Pack quantity is 5, which is a case</t>
+        </is>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 5 vs ordered ?) · Matching: brand, product name, form/spec · Not matching: pack size · Different pack quantity, but same product family and size</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>-53.34</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>-106.68</v>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>1469109</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>Pricenex</t>
+        </is>
+      </c>
+      <c r="I19" s="18" t="inlineStr">
+        <is>
+          <t>https://pricenex.com/barrier-film-4-x-6-blue-roll-of-1200-sheets/</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>Buy 5 - 9 and pay only $4.85 each, Buy 10 - 14 and pay only $4.75 each, Buy 15 - 19 and pay only $4.65 each, Buy 20 or above and pay only $4.50 each</t>
+        </is>
+      </c>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="M19" s="19" t="n">
+        <v>194.1</v>
+      </c>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="10" t="inlineStr"/>
+      <c r="B20" s="10" t="inlineStr"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
+      <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="12" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (77%)</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>JMU Dental</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>https://www.jmudental.com/products/jmu-dental-barrier-film</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Blue) · Matching: brand, form/spec, pack size · Not matching: product name · Different variant (Clear vs Blue), title and scraped_product_name disagree on variant</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>173.2</v>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="10" t="inlineStr"/>
+      <c r="B21" s="10" t="inlineStr"/>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr"/>
+      <c r="F21" s="12" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>SurgiMac Dental Supply</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>https://surgimac.com/products/4-x-6-barrier-film-blue-roll-of-1200-sheets</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>163.2</v>
+      </c>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>1126863</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>GENERIC EQUIVALENT (79%)</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Pearsonlab.com</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>https://www.pearsonlab.com/catalog/product.asp?majcatid=4547&amp;catid=7084&amp;subcatid=72363&amp;pid=76855&amp;page=1</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>GENERIC EQUIVALENT — same product type, different/no brand; no competitor sells the exact Schein house-brand item. Verify clinical equivalence before substituting.</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="M22" s="9" t="n">
+        <v>-4.84</v>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="10" t="inlineStr"/>
+      <c r="B23" s="10" t="inlineStr"/>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="12" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (53%)</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Pricenex</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>https://pricenex.com/mixing-tips-green-6-5mm-high-performance-bag-of-48/</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Yellow 4.2mm) · Matching: pack size · Not matching: brand, product name, form/spec · Different product variant and size</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="M23" s="12" t="n">
+        <v>113.36</v>
+      </c>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="10" t="inlineStr"/>
+      <c r="B24" s="10" t="inlineStr"/>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+      <c r="E24" s="10" t="inlineStr"/>
+      <c r="F24" s="12" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (62%)</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>US Dental Depot</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>https://usdentaldepot.com/mark3-high-performance-mixing-tips-mark3-1412</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Larger pack/case</t>
+        </is>
+      </c>
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 50 vs ordered 48) · Matching: product name, form/spec · Not matching: brand, pack size · Different brand and pack quantity, but same product name and variant</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>60.68</v>
+      </c>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>3250497</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>EXACT (98%)</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Pro-Health-Glide-Floss-Procter-Gamble-80779742</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="M25" s="19" t="n">
+        <v>26.85</v>
+      </c>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="10" t="inlineStr"/>
+      <c r="B26" s="10" t="inlineStr"/>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr"/>
+      <c r="E26" s="10" t="inlineStr"/>
+      <c r="F26" s="12" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (36%)</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/ez-slide-max-pack-218-yd-waxed-d-188208</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 1 vs ordered 2) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Unflavored) · Not matching: brand, product name, form/spec, pack size · Different brand and product</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>58.15</v>
+      </c>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="10" t="inlineStr"/>
+      <c r="B27" s="10" t="inlineStr"/>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr"/>
+      <c r="F27" s="12" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (38%)</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>DDS Dental Supplies</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>https://ddsdentalsupplies.com/floss-5/</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 1 vs ordered 2) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Unflavored) · Not matching: brand, product name, form/spec, pack size · Different brand and product</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>54.65</v>
+      </c>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>Frontier Dental Supply</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>https://www.frontierdental.com/us/en/product/clinpro-sealant-refill-syringes-1-2-ml-1-pk-37628</t>
+        </is>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>31.08</v>
+      </c>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="10" t="inlineStr"/>
+      <c r="B29" s="10" t="inlineStr"/>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr"/>
+      <c r="E29" s="10" t="inlineStr"/>
+      <c r="F29" s="12" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Curio.Dental</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>https://curio.dental/collections/all-products</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>page price $4.81 differs sharply from search listing $16.87 — possible wrong-variant price, verify</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="M29" s="12" t="n">
+        <v>54.78</v>
+      </c>
+    </row>
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="10" t="inlineStr"/>
+      <c r="B30" s="10" t="inlineStr"/>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
+      <c r="E30" s="10" t="inlineStr"/>
+      <c r="F30" s="12" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Tri County Dental Supply</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>https://tricountydental.com/products/3m-espe-dental-clinpro-sealnt-light-curing-low-viscosity</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: specified) · Matching: brand, form/spec, pack size · Not matching: product name · Different variant (with 10 tips) and name mismatch</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M30" s="12" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>96.47</v>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>EXACT (88%)</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>The Dentists Supply Company</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="inlineStr">
+        <is>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Equipment/Small-Equipment/Nitrous-Hoods-%26-Liners/Silhouette%C2%A0Nitrous-Oxide-Masks-and-Breathing-Circuits/p/330832-1</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="M31" s="19" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="10" t="inlineStr"/>
+      <c r="B32" s="10" t="inlineStr"/>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr"/>
+      <c r="F32" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (92%)</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Silhouette-Low-Profile-Nasal-Mask-new-SIL2-MED-12</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="M32" s="12" t="n">
+        <v>46.74</v>
+      </c>
+    </row>
+    <row r="33" ht="56" customHeight="1">
+      <c r="A33" s="10" t="inlineStr"/>
+      <c r="B33" s="10" t="inlineStr"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="12" t="n">
+        <v>141.21</v>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (36%)</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/accutron-multiuse-nasal-mask-medium-1-autoclavable-d-148801</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 1 vs ordered 12) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Medium) · Not matching: brand, product name, form/spec, pack size · Different brand and product name, also different pack quantity</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>-20.84</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>-41.68</v>
+      </c>
+    </row>
+    <row r="34" ht="56" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>5700360</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (98%)</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>The Dentists Supply Company</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-5</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M34" s="9" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="10" t="inlineStr"/>
+      <c r="B35" s="10" t="inlineStr"/>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr"/>
+      <c r="E35" s="10" t="inlineStr"/>
+      <c r="F35" s="12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (58%)</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>Davis Dental Supply</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>https://www.davisdentalsupply.com/products/productcode-d332019</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Re-stocking soon</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Strawberry) · Matching: form/spec, pack size · Not matching: brand, product name · No brand mentioned and different product name</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>13.36</v>
+      </c>
+    </row>
+    <row r="36" ht="56" customHeight="1">
+      <c r="A36" s="10" t="inlineStr"/>
+      <c r="B36" s="10" t="inlineStr"/>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr"/>
+      <c r="E36" s="10" t="inlineStr"/>
+      <c r="F36" s="12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (62%)</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/opahl-topical-anesthetic-gel-20-benzocaine-raspberry-d-131159</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="14" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Strawberry) · Matching: form/spec, pack size · Not matching: brand, product name · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="M36" s="12" t="n">
+        <v>13.28</v>
+      </c>
+    </row>
+    <row r="37" ht="56" customHeight="1">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="17" t="n">
         <v>17.61</v>
       </c>
-      <c r="F16" s="7" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>EXACT (100%)</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Supply Clinic</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>https://www.supplyclinic.com/items/3cc-luer-lock-disposable-syringes-non-sterile-box-of-100-plastcare-usa-pg-s3cc</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>1/bx</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <v>13.24</v>
-      </c>
-    </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="F17" s="17" t="n">
-        <v>30.29</v>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>EXACT (98%)</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>The Dentists Supply Company</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Preventives/Treatments-%26-Prescription-Materials/Sealants/3M-Clinpro-Sealant-Refill%2C-Syringe/p/310009-101</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed</t>
-        </is>
-      </c>
-      <c r="L17" s="17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M17" s="19" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="18" ht="56" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>5700360</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" s="12" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>EXACT (100%)</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>The Dentists Supply Company</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-5</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
-        <is>
-          <t>1/each</t>
-        </is>
-      </c>
-      <c r="K18" s="14" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="M18" s="20" t="n">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="19" ht="56" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="23" t="n">
-        <v>144.39</v>
-      </c>
-      <c r="F19" s="23" t="n">
-        <v>194.45</v>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>EXACT (98%)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>US Dental Depot</t>
-        </is>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>https://usdentaldepot.com/purevac-sc-evacuation-system-cleane-dentsply-21135</t>
-        </is>
-      </c>
-      <c r="J19" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="22" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed</t>
-        </is>
-      </c>
-      <c r="L19" s="23" t="n">
-        <v>-50.06</v>
-      </c>
-      <c r="M19" s="25" t="n">
-        <v>-100.12</v>
+      <c r="F37" s="17" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>Frontier Dental Supply</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>https://frontierdental.com/us/en/product/vista-luer-lock-syringes-3cc-100-pack-137173</t>
+        </is>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Non-Sterile) · Matching: brand, form/spec, pack size · Not matching: product name · Different brand name (Vista) but same product type</t>
+        </is>
+      </c>
+      <c r="L37" s="17" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="M37" s="19" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="38" ht="56" customHeight="1">
+      <c r="A38" s="10" t="inlineStr"/>
+      <c r="B38" s="10" t="inlineStr"/>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr"/>
+      <c r="E38" s="10" t="inlineStr"/>
+      <c r="F38" s="12" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (81%)</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/rmh3-luerlock-endo-irrigation-syringes-3cc-100-d-168420</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="14" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Non-Sterile) · Matching: brand, form/spec, pack size · Not matching: product name · Different product name (RMH3 Dental Luer-Lock Endo Irrigation Syringes) but same product family and specs</t>
+        </is>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="39" ht="56" customHeight="1">
+      <c r="A39" s="10" t="inlineStr"/>
+      <c r="B39" s="10" t="inlineStr"/>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr"/>
+      <c r="E39" s="10" t="inlineStr"/>
+      <c r="F39" s="12" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>SurgiMac Dental Supply</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>https://surgimac.com/products/luer-lock-syringe-6cc-100-bx</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="14" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Non-Sterile) · volume/size mismatch after normalization</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M39" s="12" t="n">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>
@@ -1523,6 +2436,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/OR202603121104075460_price_match.xlsx
+++ b/output/OR202603121104075460_price_match.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -166,6 +166,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -533,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -554,7 +557,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Henry Schein Price Match Negotiation  ·  Ref: OR202603121104075460  ·  Date: 03/12/2026  ·  Patient: —  ·  Generated: 2026-06-13 20:08</t>
+          <t>Henry Schein Price Match Negotiation  ·  Ref: OR202603121104075460  ·  Date: 03/12/2026  ·  Patient: —  ·  Generated: 2026-06-13 23:17</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,7 +680,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>EXACT (96%)</t>
+          <t>EXACT (92%)</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -692,7 +695,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>1 @ $267.97,  2 @ $256.98</t>
+          <t>1 unit</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -722,7 +725,7 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>APPROXIMATE (77%)</t>
+          <t>APPROXIMATE (73%)</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
@@ -737,12 +740,12 @@
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>Smaller pack size</t>
+          <t>Smaller pack size (50) than the reference product (100)</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 50 vs ordered 100) · VARIANT MISMATCH (ordered: No Flavor) · Matching: brand, product name, form/spec · Not matching: pack size · Different pack quantity (50 vs 100) and flavor (Mint vs No Flavor)</t>
+          <t>PACK MISMATCH (page 50 vs ordered 100) · VARIANT MISMATCH (ordered: No Flavor) · Matching: brand, product name, form/spec · Not matching: pack size · Different flavor (Mint) and pack quantity than the reference product</t>
         </is>
       </c>
       <c r="L5" s="12" t="n">
@@ -763,38 +766,38 @@
       <c r="D6" s="10" t="inlineStr"/>
       <c r="E6" s="10" t="inlineStr"/>
       <c r="F6" s="12" t="n">
-        <v>182.99</v>
+        <v>142.49</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (40%)</t>
+          <t>APPROXIMATE (73%)</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Top Quality Manufacturing, LLC</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/locator-replacement-denture-cap-male-assembly-10-d-178963</t>
+          <t>https://topqualitygloves.com/products/clinpro%E2%84%A2-in-office-2-1-naf-clear-fluoride-treatment</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smaller pack size (50) than the reference product (100)</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 10 vs ordered 100) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: No Flavor) · Not matching: brand, product name, form/spec, pack size · Completely different product</t>
+          <t>PACK MISMATCH (page 50 vs ordered 100) · VARIANT MISMATCH (ordered: No Flavor) · Matching: brand, product name, form/spec · Not matching: pack size · Different flavor (Mint) and pack quantity than the reference product</t>
         </is>
       </c>
       <c r="L6" s="12" t="n">
-        <v>96</v>
+        <v>136.5</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>480</v>
+        <v>682.5</v>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
@@ -820,38 +823,38 @@
         <v>222.77</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>153.9</v>
+        <v>26.99</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>GENERIC EQUIVALENT (79%)</t>
+          <t>APPROXIMATE (62%)</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Safco Dental Supply</t>
         </is>
       </c>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Perfect-Choice-Prophy-Angles-514650</t>
+          <t>https://www.safcodental.com/product/safco-cleancare-trade-disposable-prophy-angles</t>
         </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>Quantity discounts available</t>
+          <t>Smaller pack size</t>
         </is>
       </c>
       <c r="K7" s="16" t="inlineStr">
         <is>
-          <t>GENERIC EQUIVALENT — same product type, different/no brand; no competitor sells the exact Schein house-brand item. Verify clinical equivalence before substituting.</t>
+          <t>PACK MISMATCH (page 100 vs ordered 500) · Matching: product name, form/spec · Not matching: brand, pack size · Different brand, but similar product name and description</t>
         </is>
       </c>
       <c r="L7" s="17" t="n">
-        <v>68.87</v>
+        <v>195.78</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>206.61</v>
+        <v>587.34</v>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
@@ -865,38 +868,38 @@
       <c r="D8" s="10" t="inlineStr"/>
       <c r="E8" s="10" t="inlineStr"/>
       <c r="F8" s="12" t="n">
-        <v>26.99</v>
+        <v>42.99</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>APPROXIMATE (62%)</t>
+          <t>POSSIBLE (20%)</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>Safco Dental Supply</t>
+          <t>frontierdental.com</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>https://www.safcodental.com/product/safco-cleancare-trade-disposable-prophy-angles</t>
+          <t>https://frontierdental.com/us/en/product/dream-disposable-prophy-angle-latex-free-soft-100-pk-dpa100s-33009</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>Smaller pack size</t>
+          <t>Different product</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 100 vs ordered 500) · Matching: product name, form/spec · Not matching: brand, pack size · Different brand and pack quantity</t>
+          <t>PACK MISMATCH (page 64 vs ordered 500) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Soft Short Gray) · Not matching: brand, product name, form/spec, pack size · Completely different product</t>
         </is>
       </c>
       <c r="L8" s="12" t="n">
-        <v>195.78</v>
+        <v>179.78</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>587.34</v>
+        <v>539.34</v>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
@@ -914,7 +917,7 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (68%)</t>
+          <t>POSSIBLE (43%)</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -934,7 +937,7 @@
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 100 vs ordered 500) · VARIANT MISMATCH (ordered: Soft Short Gray) · Matching: brand, form/spec · Not matching: product name, pack size · Different product name and pack quantity</t>
+          <t>PACK MISMATCH (page 100 vs ordered 500) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Soft Short Gray) · Matching: brand · Not matching: product name, form/spec, pack size · Different product name and description</t>
         </is>
       </c>
       <c r="L9" s="12" t="n">
@@ -971,7 +974,7 @@
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>EXACT (100%)</t>
+          <t>EXACT (98%)</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
@@ -1012,21 +1015,21 @@
       <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="10" t="inlineStr"/>
       <c r="F11" s="12" t="n">
-        <v>7.59</v>
+        <v>7.99</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (0%)</t>
+          <t>APPROXIMATE (73%)</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>DDS Dental Supplies</t>
+          <t>skydentalsupply.com</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/preventives/</t>
+          <t>https://www.skydentalsupply.com/denture-retainer-boxes/</t>
         </is>
       </c>
       <c r="J11" s="14" t="inlineStr">
@@ -1036,14 +1039,14 @@
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 12 vs ordered 12) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Assorted) · Not matching: brand, product name, form/spec, pack size · Different product</t>
+          <t>VARIANT MISMATCH (ordered: Assorted) · Matching: brand, form/spec, pack size · Not matching: product name · Different variant (Primary Color) and brand name (Plasdent)</t>
         </is>
       </c>
       <c r="L11" s="12" t="n">
-        <v>21.87</v>
+        <v>21.47</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>328.05</v>
+        <v>322.05</v>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
@@ -1057,38 +1060,38 @@
       <c r="D12" s="10" t="inlineStr"/>
       <c r="E12" s="10" t="inlineStr"/>
       <c r="F12" s="12" t="n">
-        <v>7.85</v>
+        <v>8.18</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>EXACT (100%)</t>
+          <t>APPROXIMATE (75%)</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Frontier Dental Supply</t>
+          <t>US Dental Depot</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>https://www.frontierdental.com/us/en/product/denture-storage-boxes-assorted-12pk-100010-161115</t>
+          <t>https://usdentaldepot.com/plasdent-denture-box-assorted-chr-plasdent-200bth-xa</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>This item requires special handling - a small fee will be applied once per order during checkout.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+          <t>VARIANT MISMATCH (ordered: Assorted) · Matching: brand, form/spec, pack size · Not matching: product name · Different variant (Chroma Colored) and brand name (PLASDENT)</t>
         </is>
       </c>
       <c r="L12" s="12" t="n">
-        <v>21.61</v>
+        <v>21.28</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>324.15</v>
+        <v>319.2</v>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
@@ -1114,21 +1117,21 @@
         <v>82.19</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>58.27</v>
+        <v>64.89</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>EXACT (92%)</t>
+          <t>EXACT (98%)</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/luxatemp-plus-mixing-tips-fine-25-bx-dmg-america-110351</t>
+          <t>https://www.net32.com/ec/luxatemp-automix-plus-fine-mixing-tips-25-d-45565</t>
         </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
@@ -1142,10 +1145,10 @@
         </is>
       </c>
       <c r="L13" s="17" t="n">
-        <v>23.92</v>
+        <v>17.3</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>95.68000000000001</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
@@ -1159,11 +1162,11 @@
       <c r="D14" s="10" t="inlineStr"/>
       <c r="E14" s="10" t="inlineStr"/>
       <c r="F14" s="12" t="n">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (51%)</t>
+          <t>POSSIBLE (66%)</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -1183,14 +1186,14 @@
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Fine) · Matching: pack size · Not matching: brand, product name, form/spec · Different brand and product name</t>
+          <t>VARIANT MISMATCH (ordered: Fine) · Matching: form/spec, pack size · Not matching: brand, product name · Different brand and product name</t>
         </is>
       </c>
       <c r="L14" s="12" t="n">
-        <v>70.2</v>
+        <v>77.2</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>280.8</v>
+        <v>308.8</v>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
@@ -1204,38 +1207,38 @@
       <c r="D15" s="10" t="inlineStr"/>
       <c r="E15" s="10" t="inlineStr"/>
       <c r="F15" s="12" t="n">
-        <v>13.99</v>
+        <v>33.99</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (36%)</t>
+          <t>POSSIBLE (47%)</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>oktowallz.com</t>
+          <t>tdsc.com</t>
         </is>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>https://oktowallz.com/view/Orange-Pack-Of-49-Disposable-Tips-For-Dental-Impression/833810</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Dispensing-%26-Mixing-Products/Dispensing-Products/Mixing-Tips/c/539</t>
         </is>
       </c>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Larger pack</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 49 vs ordered 25) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Fine) · Not matching: brand, product name, form/spec, pack size · Different product and pack quantity</t>
+          <t>PACK MISMATCH (page 48 vs ordered 25) · VARIANT MISMATCH (ordered: Fine) · Matching: form/spec · Not matching: brand, product name, pack size · Different brand, product name, and pack quantity</t>
         </is>
       </c>
       <c r="L15" s="12" t="n">
-        <v>68.2</v>
+        <v>48.2</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>272.8</v>
+        <v>192.8</v>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
@@ -1265,7 +1268,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>EXACT (100%)</t>
+          <t>EXACT (98%)</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1330,7 +1333,7 @@
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: specified) · Matching: pack size · Not matching: brand, product name, form/spec · Different brand and product name, also variant 'Sable' does not match</t>
+          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: specified) · Matching: pack size · Not matching: brand, product name, form/spec · Different brand and product name</t>
         </is>
       </c>
       <c r="L17" s="12" t="n">
@@ -1351,38 +1354,38 @@
       <c r="D18" s="10" t="inlineStr"/>
       <c r="E18" s="10" t="inlineStr"/>
       <c r="F18" s="12" t="n">
-        <v>197.73</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>APPROXIMATE (77%)</t>
+          <t>POSSIBLE (0%)</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>crazydentalprices.com</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>https://www.dentalcity.com/product/11656/dentsply-sirona-purevac-sc-evacuation-system-cleaner-5l</t>
+          <t>https://www.crazydentalprices.com/Purevac-SC-21132</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>Pack quantity is 5, which is a case</t>
+          <t>Buy 4 Get 1 Free! (Limit 5)</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 5 vs ordered ?) · Matching: brand, product name, form/spec · Not matching: pack size · Different pack quantity, but same product family and size</t>
+          <t>volume/size mismatch after normalization</t>
         </is>
       </c>
       <c r="L18" s="12" t="n">
-        <v>-53.34</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>-106.68</v>
+        <v>147.8</v>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
@@ -1427,7 +1430,7 @@
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>Buy 5 - 9 and pay only $4.85 each, Buy 10 - 14 and pay only $4.75 each, Buy 15 - 19 and pay only $4.65 each, Buy 20 or above and pay only $4.50 each</t>
+          <t>Buy 5 - 9 and pay only $4.85 each; Buy 10 - 14 and pay only $4.75 each; Buy 15 - 19 and pay only $4.65 each; Buy 20 or above and pay only $4.50 each</t>
         </is>
       </c>
       <c r="K19" s="16" t="inlineStr">
@@ -1477,7 +1480,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>VARIANT MISMATCH (ordered: Blue) · Matching: brand, form/spec, pack size · Not matching: product name · Different variant (Clear vs Blue), title and scraped_product_name disagree on variant</t>
+          <t>VARIANT MISMATCH (ordered: Blue) · Matching: brand, form/spec, pack size · Not matching: product name · Variant mismatch: Blue vs Clear</t>
         </is>
       </c>
       <c r="L20" s="12" t="n">
@@ -1498,7 +1501,7 @@
       <c r="D21" s="10" t="inlineStr"/>
       <c r="E21" s="10" t="inlineStr"/>
       <c r="F21" s="12" t="n">
-        <v>7.99</v>
+        <v>11.99</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
@@ -1507,17 +1510,17 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>SurgiMac Dental Supply</t>
+          <t>skydentalsupply.com</t>
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
-          <t>https://surgimac.com/products/4-x-6-barrier-film-blue-roll-of-1200-sheets</t>
+          <t>https://www.skydentalsupply.com/100z-barrier-film.htm</t>
         </is>
       </c>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
@@ -1526,67 +1529,67 @@
         </is>
       </c>
       <c r="L21" s="12" t="n">
-        <v>16.32</v>
+        <v>12.32</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>163.2</v>
+        <v>123.2</v>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>1126863</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>34.29</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>GENERIC EQUIVALENT (79%)</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>Pearsonlab.com</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>https://www.pearsonlab.com/catalog/product.asp?majcatid=4547&amp;catid=7084&amp;subcatid=72363&amp;pid=76855&amp;page=1</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>97</v>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>GENERIC EQUIVALENT (81%)</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Silhouette-Low-Profile-Nasal-Mask-new-SIL2-MED-12</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>No minimum order required</t>
+        </is>
+      </c>
+      <c r="K22" s="16" t="inlineStr">
         <is>
           <t>GENERIC EQUIVALENT — same product type, different/no brand; no competitor sells the exact Schein house-brand item. Verify clinical equivalence before substituting.</t>
         </is>
       </c>
-      <c r="L22" s="7" t="n">
-        <v>-1.21</v>
-      </c>
-      <c r="M22" s="9" t="n">
-        <v>-4.84</v>
+      <c r="L22" s="17" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="M22" s="19" t="n">
+        <v>46.74</v>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
@@ -1600,38 +1603,38 @@
       <c r="D23" s="10" t="inlineStr"/>
       <c r="E23" s="10" t="inlineStr"/>
       <c r="F23" s="12" t="n">
-        <v>5.95</v>
+        <v>44.62</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (53%)</t>
+          <t>POSSIBLE (62%)</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Pricenex</t>
+          <t>frischsnwo.com</t>
         </is>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>https://pricenex.com/mixing-tips-green-6-5mm-high-performance-bag-of-48/</t>
+          <t>https://frischsnwo.com/listing/porter-sil2-med-12-silhouette-2-low-profile-nasal-hood-masks</t>
         </is>
       </c>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>single unit</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Yellow 4.2mm) · Matching: pack size · Not matching: brand, product name, form/spec · Different product variant and size</t>
+          <t>PACK MISMATCH (page 1 vs ordered 12) · VARIANT MISMATCH (ordered: Medium) · Matching: brand, form/spec · Not matching: product name, pack size · different product name and pack quantity</t>
         </is>
       </c>
       <c r="L23" s="12" t="n">
-        <v>28.34</v>
+        <v>75.75</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>113.36</v>
+        <v>151.5</v>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
@@ -1645,95 +1648,95 @@
       <c r="D24" s="10" t="inlineStr"/>
       <c r="E24" s="10" t="inlineStr"/>
       <c r="F24" s="12" t="n">
-        <v>19.12</v>
+        <v>111.6</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>APPROXIMATE (62%)</t>
+          <t>POSSIBLE (79%)</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>US Dental Depot</t>
+          <t>Prime Dental Supply</t>
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>https://usdentaldepot.com/mark3-high-performance-mixing-tips-mark3-1412</t>
+          <t>https://www.primedentalsupply.com/silhouette-mask-variety-12-pack-3-of-each-size-pediatric-small-medium-large-porter-sil2-var-4x3</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>Larger pack/case</t>
+          <t>This item is ineligible for the coupon code.</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 50 vs ordered 48) · Matching: product name, form/spec · Not matching: brand, pack size · Different brand and pack quantity, but same product name and variant</t>
+          <t>VARIANT MISMATCH (ordered: Medium) · Matching: brand, form/spec, pack size · Not matching: product name · different variant (variety pack instead of medium)</t>
         </is>
       </c>
       <c r="L24" s="12" t="n">
-        <v>15.17</v>
+        <v>8.77</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>60.68</v>
+        <v>17.54</v>
       </c>
     </row>
     <row r="25" ht="56" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>3250497</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>16.62</v>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>EXACT (98%)</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>Crazy Dental Price Club</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>https://www.crazydentalprices.com/Pro-Health-Glide-Floss-Procter-Gamble-80779742</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed</t>
-        </is>
-      </c>
-      <c r="L25" s="17" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="M25" s="19" t="n">
-        <v>26.85</v>
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>1126863</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>GENERIC EQUIVALENT (73%)</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>jobs.pfefferwerk.de</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>https://jobs.pfefferwerk.de/products/practicon-hp-universal-mixing-tips-yellow-42mm-pack-of-48</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>No minimum order required.</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>GENERIC EQUIVALENT — same product type, different/no brand; no competitor sells the exact Schein house-brand item. Verify clinical equivalence before substituting.</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M25" s="20" t="n">
+        <v>5.2</v>
       </c>
     </row>
     <row r="26" ht="56" customHeight="1">
@@ -1747,21 +1750,21 @@
       <c r="D26" s="10" t="inlineStr"/>
       <c r="E26" s="10" t="inlineStr"/>
       <c r="F26" s="12" t="n">
-        <v>4.99</v>
+        <v>5.95</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (36%)</t>
+          <t>POSSIBLE (51%)</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Pricenex</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/ez-slide-max-pack-218-yd-waxed-d-188208</t>
+          <t>https://pricenex.com/mixing-tips-green-6-5mm-high-performance-bag-of-48/</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
@@ -1771,14 +1774,14 @@
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 1 vs ordered 2) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Unflavored) · Not matching: brand, product name, form/spec, pack size · Different brand and product</t>
+          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Yellow 4.2mm) · Matching: pack size · Not matching: brand, product name, form/spec · Different product variant and size</t>
         </is>
       </c>
       <c r="L26" s="12" t="n">
-        <v>11.63</v>
+        <v>28.34</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>58.15</v>
+        <v>113.36</v>
       </c>
     </row>
     <row r="27" ht="56" customHeight="1">
@@ -1792,38 +1795,38 @@
       <c r="D27" s="10" t="inlineStr"/>
       <c r="E27" s="10" t="inlineStr"/>
       <c r="F27" s="12" t="n">
-        <v>5.69</v>
+        <v>19.12</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (38%)</t>
+          <t>POSSIBLE (47%)</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>DDS Dental Supplies</t>
+          <t>US Dental Depot</t>
         </is>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/floss-5/</t>
+          <t>https://usdentaldepot.com/mark3-high-performance-mixing-tips-mark3-1412</t>
         </is>
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Larger pack</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 1 vs ordered 2) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Unflavored) · Not matching: brand, product name, form/spec, pack size · Different brand and product</t>
+          <t>PACK MISMATCH (page 50 vs ordered 48) · VARIANT MISMATCH (ordered: Yellow 4.2mm) · Matching: form/spec · Not matching: brand, product name, pack size · Different brand and product name, larger pack quantity</t>
         </is>
       </c>
       <c r="L27" s="12" t="n">
-        <v>10.93</v>
+        <v>15.17</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>54.65</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="28" ht="56" customHeight="1">
@@ -1884,48 +1887,60 @@
       </c>
     </row>
     <row r="29" ht="56" customHeight="1">
-      <c r="A29" s="10" t="inlineStr"/>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr"/>
-      <c r="E29" s="10" t="inlineStr"/>
-      <c r="F29" s="12" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>POSSIBLE (0%)</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>Curio.Dental</t>
-        </is>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>https://curio.dental/collections/all-products</t>
-        </is>
-      </c>
-      <c r="J29" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K29" s="14" t="inlineStr">
-        <is>
-          <t>page price $4.81 differs sharply from search listing $16.87 — possible wrong-variant price, verify</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>27.39</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>54.78</v>
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>3250497</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>EXACT (98%)</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Pro-Health-Glide-Floss-Procter-Gamble-80779742</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L29" s="17" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="M29" s="19" t="n">
+        <v>26.85</v>
       </c>
     </row>
     <row r="30" ht="56" customHeight="1">
@@ -1933,146 +1948,146 @@
       <c r="B30" s="10" t="inlineStr"/>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ Option 3</t>
+          <t xml:space="preserve">   ↳ Option 2</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr"/>
       <c r="E30" s="10" t="inlineStr"/>
       <c r="F30" s="12" t="n">
-        <v>25.95</v>
+        <v>12.99</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>APPROXIMATE (77%)</t>
+          <t>POSSIBLE (64%)</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>Tri County Dental Supply</t>
+          <t>skydentalsupply.com</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>https://tricountydental.com/products/3m-espe-dental-clinpro-sealnt-light-curing-low-viscosity</t>
+          <t>https://www.skydentalsupply.com/oral-b-glide-floss-.htm</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Single pack</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>VARIANT MISMATCH (ordered: specified) · Matching: brand, form/spec, pack size · Not matching: product name · Different variant (with 10 tips) and name mismatch</t>
+          <t>PACK MISMATCH (page 1 vs ordered 2) · VARIANT MISMATCH (ordered: Unflavored) · Matching: brand, form/spec · Not matching: product name, pack size · Different product variant and pack quantity</t>
         </is>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6.25</v>
+        <v>3.63</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>12.5</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="31" ht="56" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>1459489</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="n">
+      <c r="A31" s="10" t="inlineStr"/>
+      <c r="B31" s="10" t="inlineStr"/>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
+      <c r="E31" s="10" t="inlineStr"/>
+      <c r="F31" s="12" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (96%)</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>optimusdentalsupply.com</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>https://optimusdentalsupply.com/preventives/p-g-oral-b-glide-pro-health-floss-original-font-refills-unwaxed-unflavored-160m-spool-2-bx/</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>13.85</v>
+      </c>
+    </row>
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="17" t="n">
-        <v>120.37</v>
-      </c>
-      <c r="F31" s="17" t="n">
-        <v>96.47</v>
-      </c>
-      <c r="G31" s="15" t="inlineStr">
-        <is>
-          <t>EXACT (88%)</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="inlineStr">
-        <is>
-          <t>The Dentists Supply Company</t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Equipment/Small-Equipment/Nitrous-Hoods-%26-Liners/Silhouette%C2%A0Nitrous-Oxide-Masks-and-Breathing-Circuits/p/330832-1</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K31" s="16" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed</t>
-        </is>
-      </c>
-      <c r="L31" s="17" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="M31" s="19" t="n">
-        <v>47.8</v>
-      </c>
-    </row>
-    <row r="32" ht="56" customHeight="1">
-      <c r="A32" s="10" t="inlineStr"/>
-      <c r="B32" s="10" t="inlineStr"/>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr"/>
-      <c r="E32" s="10" t="inlineStr"/>
-      <c r="F32" s="12" t="n">
-        <v>97</v>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>EXACT (92%)</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>Crazy Dental Price Club</t>
-        </is>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>https://www.crazydentalprices.com/Silhouette-Low-Profile-Nasal-Mask-new-SIL2-MED-12</t>
-        </is>
-      </c>
-      <c r="J32" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K32" s="14" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
-        </is>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>23.37</v>
-      </c>
-      <c r="M32" s="12" t="n">
-        <v>46.74</v>
+      <c r="E32" s="17" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>EXACT · VARIANT UNVERIFIED (92%)</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>amerdental.com</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="inlineStr">
+        <is>
+          <t>https://amerdental.com/collections/exam-hygiene/products/luer-lock-syringes-3cc</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="16" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed · VARIANT UNVERIFIED — page did not confirm the ordered variant (Non-Sterile); verify before buying</t>
+        </is>
+      </c>
+      <c r="L32" s="17" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="M32" s="19" t="n">
+        <v>13.32</v>
       </c>
     </row>
     <row r="33" ht="56" customHeight="1">
@@ -2080,27 +2095,27 @@
       <c r="B33" s="10" t="inlineStr"/>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ Option 3</t>
+          <t xml:space="preserve">   ↳ Option 2</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr"/>
       <c r="E33" s="10" t="inlineStr"/>
       <c r="F33" s="12" t="n">
-        <v>141.21</v>
+        <v>10.99</v>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (36%)</t>
+          <t>APPROXIMATE (77%)</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>net32.com</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/accutron-multiuse-nasal-mask-medium-1-autoclavable-d-148801</t>
+          <t>https://www.net32.com/ec/maxill-luer-lock-standard-syringe-3-cc-d-178103</t>
         </is>
       </c>
       <c r="J33" s="14" t="inlineStr">
@@ -2110,116 +2125,116 @@
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 1 vs ordered 12) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Medium) · Not matching: brand, product name, form/spec, pack size · Different brand and product name, also different pack quantity</t>
+          <t>VARIANT MISMATCH (ordered: Non-Sterile) · Matching: brand, form/spec, pack size · Not matching: product name · Different brand name, but same product type</t>
         </is>
       </c>
       <c r="L33" s="12" t="n">
-        <v>-20.84</v>
+        <v>6.62</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>-41.68</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="34" ht="56" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr"/>
+      <c r="B34" s="10" t="inlineStr"/>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr"/>
+      <c r="E34" s="10" t="inlineStr"/>
+      <c r="F34" s="12" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>EXACT · VARIANT UNVERIFIED (96%)</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Medex Supply</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>https://medexsupply.com/syringe-3cc-luer-lock-w-o-needle-100-bx/</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed · VARIANT UNVERIFIED — page did not confirm the ordered variant (Non-Sterile); verify before buying (alternate source, higher price than Option 1)</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>5700360</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D35" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E34" s="7" t="n">
+      <c r="E35" s="12" t="n">
         <v>6.29</v>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F35" s="12" t="n">
         <v>6.5</v>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>EXACT (98%)</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (96%)</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>The Dentists Supply Company</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I35" s="13" t="inlineStr">
         <is>
           <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-5</t>
         </is>
       </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr">
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
         <is>
           <t>Exact — all four trust criteria confirmed</t>
         </is>
       </c>
-      <c r="L34" s="7" t="n">
+      <c r="L35" s="12" t="n">
         <v>-0.21</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M35" s="20" t="n">
         <v>-0.84</v>
-      </c>
-    </row>
-    <row r="35" ht="56" customHeight="1">
-      <c r="A35" s="10" t="inlineStr"/>
-      <c r="B35" s="10" t="inlineStr"/>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr"/>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="12" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>POSSIBLE (58%)</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>Davis Dental Supply</t>
-        </is>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>https://www.davisdentalsupply.com/products/productcode-d332019</t>
-        </is>
-      </c>
-      <c r="J35" s="14" t="inlineStr">
-        <is>
-          <t>Re-stocking soon</t>
-        </is>
-      </c>
-      <c r="K35" s="14" t="inlineStr">
-        <is>
-          <t>VARIANT MISMATCH (ordered: Strawberry) · Matching: form/spec, pack size · Not matching: brand, product name · No brand mentioned and different product name</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>13.36</v>
       </c>
     </row>
     <row r="36" ht="56" customHeight="1">
@@ -2227,13 +2242,13 @@
       <c r="B36" s="10" t="inlineStr"/>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ Option 3</t>
+          <t xml:space="preserve">   ↳ Option 2</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr"/>
       <c r="E36" s="10" t="inlineStr"/>
       <c r="F36" s="12" t="n">
-        <v>2.97</v>
+        <v>3.99</v>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
@@ -2247,12 +2262,12 @@
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/opahl-topical-anesthetic-gel-20-benzocaine-raspberry-d-131159</t>
+          <t>https://www.net32.com/ec/primo-topical-benzocaine-gel-20-strawberry-1oz-d-161921</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 @ $3.99, 6 @ $3.75</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
@@ -2261,157 +2276,55 @@
         </is>
       </c>
       <c r="L36" s="12" t="n">
-        <v>3.32</v>
+        <v>2.3</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>13.28</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="37" ht="56" customHeight="1">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>5701400</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>17.61</v>
-      </c>
-      <c r="F37" s="17" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>APPROXIMATE (77%)</t>
-        </is>
-      </c>
-      <c r="H37" s="15" t="inlineStr">
-        <is>
-          <t>Frontier Dental Supply</t>
-        </is>
-      </c>
-      <c r="I37" s="18" t="inlineStr">
-        <is>
-          <t>https://frontierdental.com/us/en/product/vista-luer-lock-syringes-3cc-100-pack-137173</t>
-        </is>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K37" s="16" t="inlineStr">
-        <is>
-          <t>VARIANT MISMATCH (ordered: Non-Sterile) · Matching: brand, form/spec, pack size · Not matching: product name · Different brand name (Vista) but same product type</t>
-        </is>
-      </c>
-      <c r="L37" s="17" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="M37" s="19" t="n">
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="38" ht="56" customHeight="1">
-      <c r="A38" s="10" t="inlineStr"/>
-      <c r="B38" s="10" t="inlineStr"/>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr"/>
-      <c r="E38" s="10" t="inlineStr"/>
-      <c r="F38" s="12" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>APPROXIMATE (81%)</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>Net32</t>
-        </is>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>https://www.net32.com/ec/rmh3-luerlock-endo-irrigation-syringes-3cc-100-d-168420</t>
-        </is>
-      </c>
-      <c r="J38" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K38" s="14" t="inlineStr">
-        <is>
-          <t>VARIANT MISMATCH (ordered: Non-Sterile) · Matching: brand, form/spec, pack size · Not matching: product name · Different product name (RMH3 Dental Luer-Lock Endo Irrigation Syringes) but same product family and specs</t>
-        </is>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>6.72</v>
-      </c>
-    </row>
-    <row r="39" ht="56" customHeight="1">
-      <c r="A39" s="10" t="inlineStr"/>
-      <c r="B39" s="10" t="inlineStr"/>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr"/>
+      <c r="B37" s="10" t="inlineStr"/>
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   ↳ Option 3</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr"/>
-      <c r="E39" s="10" t="inlineStr"/>
-      <c r="F39" s="12" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>POSSIBLE (0%)</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>SurgiMac Dental Supply</t>
-        </is>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>https://surgimac.com/products/luer-lock-syringe-6cc-100-bx</t>
-        </is>
-      </c>
-      <c r="J39" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K39" s="14" t="inlineStr">
-        <is>
-          <t>VARIANT MISMATCH (ordered: Non-Sterile) · volume/size mismatch after normalization</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>1.24</v>
+      <c r="D37" s="10" t="inlineStr"/>
+      <c r="E37" s="10" t="inlineStr"/>
+      <c r="F37" s="12" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (62%)</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>surgimac.com</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>https://surgimac.com/products/strawberry-flavored-topical-anesthetic-gel-benzocaine-20-1-oz</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Strawberry) · Matching: form/spec, pack size · Not matching: brand, product name · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2454,8 +2367,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
